--- a/results/breakdown/2050/nitrous oxide production, AON 90 membrane, fossil ammonia.xlsx
+++ b/results/breakdown/2050/nitrous oxide production, AON 90 membrane, fossil ammonia.xlsx
@@ -426,7 +426,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>2.975197044363919</v>
+        <v>2.975197044363924</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -443,7 +443,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>2.940316955600744</v>
+        <v>2.940316955600752</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -460,7 +460,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.000435947543100294</v>
+        <v>0.0004359475431002956</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -477,7 +477,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.0004444324304989023</v>
+        <v>0.0004444324304988945</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -494,7 +494,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>1.565136787828558E-05</v>
+        <v>1.565136787828526E-05</v>
       </c>
       <c r="E6">
         <v>1</v>
